--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -501,19 +501,19 @@
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>声音</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>移动网络与SIM卡</t>
+          <t>安全</t>
         </is>
       </c>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>声音</t>
+          <t>移动网络与SIM卡</t>
         </is>
       </c>
       <c r="L1" s="2" t="n"/>
@@ -663,34 +663,34 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
+          <t>朗读速度</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>query_speech_rate()
+set_speech_rate(value)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
           <t>锁屏方式</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>query_lock_screen_method()
 (安全验证，不可自动化)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>默认数据卡</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>query_default_data_card()</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>朗读速度</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>query_speech_rate()
-set_speech_rate(value)</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -763,34 +763,34 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
+          <t>来电铃声</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>query_ringtone()
+set_ringtone_default()</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
           <t>锁屏密码</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>set_lock_screen_password(password)</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>SIM卡状态</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>query_sim_status()
 query_sim_carrier()</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>来电铃声</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>query_ringtone()
-set_ringtone_default()</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -844,28 +844,36 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
+          <t>信息铃声</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>query_message_ringtone()</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
           <t>指纹录入状态</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>query_fingerprint()
 (录入需物理传感器)</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>SIM卡使用状态</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>query_sim_enabled(card)
 set_sim_enabled(card, 'on'/'off')</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr"/>
-      <c r="L5" s="5" t="inlineStr"/>
       <c r="M5" s="5" t="inlineStr"/>
       <c r="N5" s="5" t="inlineStr"/>
       <c r="O5" s="5" t="inlineStr"/>
@@ -910,17 +918,25 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>通知铃声</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>query_notification_ringtone()</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>隐私空间</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>query_privacy_space()
 set_privacy_space(main_pwd, space_pwd)</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="5" t="inlineStr"/>
       <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -979,8 +979,17 @@
           <t>query_ebook_mode()</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>响铃时振动</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>query_ring_vibration()
+set_ring_vibration('on'/'off')</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1047,7 +1047,8 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>query_personal_hotspot()</t>
+          <t>query_personal_hotspot()
+set_personal_hotspot('on'/'off')</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1117,13 +1118,12 @@
     <row r="11" ht="50" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>网络加速</t>
+          <t>已连接设备</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>query_network_acceleration()
-set_network_acceleration('on'/'off')</t>
+          <t>query_hotspot_connected_devices()</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1154,13 +1154,12 @@
     <row r="12" ht="50" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>NFC</t>
+          <t>AP 频段</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>query_nfc()
-set_nfc('on'/'off')</t>
+          <t>query_hotspot_ap_band()</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1192,13 +1191,13 @@
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>默认付款应用</t>
+          <t>USB 共享网络</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>query_default_payment_app()
-set_default_payment_app(app_name)</t>
+          <t>query_usb_tethering()
+set_usb_tethering('on'/'off')</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1226,6 +1225,93 @@
       <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>网络加速</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>query_network_acceleration()
+set_network_acceleration('on'/'off')</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr"/>
+      <c r="D14" s="5" t="inlineStr"/>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr"/>
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="5" t="inlineStr"/>
+      <c r="N14" s="5" t="inlineStr"/>
+      <c r="O14" s="5" t="inlineStr"/>
+      <c r="P14" s="5" t="inlineStr"/>
+      <c r="Q14" s="5" t="inlineStr"/>
+      <c r="R14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>NFC</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>query_nfc()
+set_nfc('on'/'off')</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr"/>
+      <c r="D15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr"/>
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
+      <c r="O15" s="5" t="inlineStr"/>
+      <c r="P15" s="5" t="inlineStr"/>
+      <c r="Q15" s="5" t="inlineStr"/>
+      <c r="R15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>默认付款应用</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>query_default_payment_app()
+set_default_payment_app(app_name)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr"/>
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="5" t="inlineStr"/>
+      <c r="N16" s="5" t="inlineStr"/>
+      <c r="O16" s="5" t="inlineStr"/>
+      <c r="P16" s="5" t="inlineStr"/>
+      <c r="Q16" s="5" t="inlineStr"/>
+      <c r="R16" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -507,13 +507,13 @@
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>移动网络与SIM卡</t>
         </is>
       </c>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>移动网络与SIM卡</t>
+          <t>安全</t>
         </is>
       </c>
       <c r="L1" s="2" t="n"/>
@@ -674,25 +674,25 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>默认数据卡</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>query_default_data_card()</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
           <t>锁屏方式</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>query_lock_screen_method()
 (安全验证，不可自动化)</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>默认数据卡</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>query_default_data_card()</t>
-        </is>
-      </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
           <t>放大手势</t>
@@ -774,23 +774,23 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>锁屏密码</t>
+          <t>SIM卡状态</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>set_lock_screen_password(password)</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>SIM卡状态</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>query_sim_status()
 query_sim_carrier()</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>锁屏密码</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>set_lock_screen_password(password)</t>
         </is>
       </c>
       <c r="M4" s="4" t="inlineStr">
@@ -854,24 +854,24 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
+          <t>SIM卡使用状态</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>query_sim_enabled(card)
+set_sim_enabled(card, 'on'/'off')</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
           <t>指纹录入状态</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>query_fingerprint()
 (录入需物理传感器)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>SIM卡使用状态</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>query_sim_enabled(card)
-set_sim_enabled(card, 'on'/'off')</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr"/>
@@ -928,17 +928,26 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
+          <t>应用联网</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>query_app_network_access(app_name)
+set_app_network_access(app_name, type, 'on'/'off')</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
           <t>隐私空间</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>query_privacy_space()
 set_privacy_space(main_pwd, space_pwd)</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr"/>
-      <c r="L6" s="5" t="inlineStr"/>
       <c r="M6" s="5" t="inlineStr"/>
       <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -495,19 +495,19 @@
       <c r="D1" s="2" t="n"/>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>显示与亮度</t>
+          <t>移动网络与SIM卡</t>
         </is>
       </c>
       <c r="F1" s="2" t="n"/>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>声音</t>
+          <t>显示与亮度</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>移动网络与SIM卡</t>
+          <t>声音</t>
         </is>
       </c>
       <c r="J1" s="2" t="n"/>
@@ -653,35 +653,35 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
+          <t>默认数据卡</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>query_default_data_card()</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
           <t>屏幕亮度</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>query_brightness() →百分比</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>朗读速度</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>query_speech_rate()
 set_speech_rate(value)</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>默认数据卡</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>query_default_data_card()</t>
-        </is>
-      </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>锁屏方式</t>
@@ -752,35 +752,35 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>SIM卡状态</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>query_sim_status()
+query_sim_carrier()</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>自动调节亮度</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>query_auto_brightness()
 set_auto_brightness('on'/'off')</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>来电铃声</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>query_ringtone()
 set_ringtone_default()</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>SIM卡状态</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>query_sim_status()
-query_sim_carrier()</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -833,34 +833,34 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
+          <t>SIM卡使用状态</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>query_sim_enabled(card)
+set_sim_enabled(card, 'on'/'off')</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
           <t>字体大小</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>query_font_size()
 set_font_size('小'/'标准'/'大'/'超大')</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>信息铃声</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>query_message_ringtone()</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>SIM卡使用状态</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>query_sim_enabled(card)
-set_sim_enabled(card, 'on'/'off')</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -907,34 +907,34 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
+          <t>应用联网</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>query_app_network_access(app_name)
+set_app_network_access(app_name, type, 'on'/'off')</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
           <t>字体粗细</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>query_font_weight()
 set_font_weight('最细'/'标准'/'最粗')</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>通知铃声</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>query_notification_ringtone()</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>应用联网</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>query_app_network_access(app_name)
-set_app_network_access(app_name, type, 'on'/'off')</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -980,27 +980,35 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>应用流量使用量</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>query_app_data_usage(app_name, period='30d'/'24h')</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
           <t>电子书模式</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>query_ebook_mode()</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>响铃时振动</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>query_ring_vibration()
 set_ring_vibration('on'/'off')</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr"/>
-      <c r="J7" s="5" t="inlineStr"/>
       <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="5" t="inlineStr"/>
       <c r="M7" s="5" t="inlineStr"/>

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -658,7 +658,8 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>query_default_data_card()</t>
+          <t>query_default_data_card()
+set_default_data_card('1'/'2')</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -959,13 +959,13 @@
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>星闪</t>
+          <t>蓝牙本机名称</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>query_nearlink()
-set_nearlink('on'/'off')</t>
+          <t>query_bluetooth_name()
+set_bluetooth_name(name)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1022,13 +1022,13 @@
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>飞行模式</t>
+          <t>星闪</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>query_flight_mode()
-set_flight_mode('on'/'off')</t>
+          <t>query_nearlink()
+set_nearlink('on'/'off')</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -1060,13 +1060,13 @@
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>个人热点</t>
+          <t>飞行模式</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>query_personal_hotspot()
-set_personal_hotspot('on'/'off')</t>
+          <t>query_flight_mode()
+set_flight_mode('on'/'off')</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1097,14 +1097,13 @@
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>热点配置</t>
+          <t>个人热点</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>query_hotspot_config()
-set_hotspot_name(name)
-set_hotspot_password(pwd)</t>
+          <t>query_personal_hotspot()
+set_personal_hotspot('on'/'off')</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1136,12 +1135,14 @@
     <row r="11" ht="50" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>已连接设备</t>
+          <t>热点配置</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>query_hotspot_connected_devices()</t>
+          <t>query_hotspot_config()
+set_hotspot_name(name)
+set_hotspot_password(pwd)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1172,12 +1173,12 @@
     <row r="12" ht="50" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>AP 频段</t>
+          <t>已连接设备</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>query_hotspot_ap_band()</t>
+          <t>query_hotspot_connected_devices()</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1209,13 +1210,12 @@
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>USB 共享网络</t>
+          <t>AP 频段</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>query_usb_tethering()
-set_usb_tethering('on'/'off')</t>
+          <t>query_hotspot_ap_band()</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1247,13 +1247,13 @@
     <row r="14" ht="50" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>网络加速</t>
+          <t>USB 共享网络</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>query_network_acceleration()
-set_network_acceleration('on'/'off')</t>
+          <t>query_usb_tethering()
+set_usb_tethering('on'/'off')</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
@@ -1276,13 +1276,13 @@
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>NFC</t>
+          <t>网络加速</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>query_nfc()
-set_nfc('on'/'off')</t>
+          <t>query_network_acceleration()
+set_network_acceleration('on'/'off')</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
     <row r="16" ht="50" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>默认付款应用</t>
+          <t>NFC</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>query_default_payment_app()
-set_default_payment_app(app_name)</t>
+          <t>query_nfc()
+set_nfc('on'/'off')</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
@@ -1331,6 +1331,35 @@
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
     </row>
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>默认付款应用</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>query_default_payment_app()
+set_default_payment_app(app_name)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr"/>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr"/>
+      <c r="K17" s="5" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr"/>
+      <c r="M17" s="5" t="inlineStr"/>
+      <c r="N17" s="5" t="inlineStr"/>
+      <c r="O17" s="5" t="inlineStr"/>
+      <c r="P17" s="5" t="inlineStr"/>
+      <c r="Q17" s="5" t="inlineStr"/>
+      <c r="R17" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="Q1:R1"/>

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -478,6 +478,8 @@
     <col width="30" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -525,16 +527,22 @@
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>电池</t>
+          <t>桌面设置</t>
         </is>
       </c>
       <c r="P1" s="2" t="n"/>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>电池</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>通知与免打扰</t>
         </is>
       </c>
-      <c r="R1" s="2" t="n"/>
+      <c r="T1" s="2" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -623,6 +631,16 @@
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>设置项</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -707,21 +725,34 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
+          <t>桌面设置(下滑/上滑/布局/自动对齐/锁定布局)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>query_desktop_setting(item)
+set_desktop_setting(item, 'on'/'off')
+set_desktop_layout('标准'/'紧凑')
+  item: swipe_down/swipe_up/layout/auto_align/lock_layout</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
           <t>省电模式</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="R3" s="4" t="inlineStr">
         <is>
           <t>query_power_saving()
 set_power_saving('on'/'off')</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="S3" s="4" t="inlineStr">
         <is>
           <t>勿扰模式</t>
         </is>
       </c>
-      <c r="R3" s="4" t="inlineStr">
+      <c r="T3" s="4" t="inlineStr">
         <is>
           <t>query_dnd()
 set_dnd('on'/'off')</t>
@@ -809,6 +840,8 @@
       <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
     </row>
     <row r="5" ht="50" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -881,6 +914,8 @@
       <c r="P5" s="5" t="inlineStr"/>
       <c r="Q5" s="5" t="inlineStr"/>
       <c r="R5" s="5" t="inlineStr"/>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
     </row>
     <row r="6" ht="50" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -955,6 +990,8 @@
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
       <c r="R6" s="5" t="inlineStr"/>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="50" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -1018,6 +1055,8 @@
       <c r="P7" s="5" t="inlineStr"/>
       <c r="Q7" s="5" t="inlineStr"/>
       <c r="R7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -1056,6 +1095,8 @@
       <c r="P8" s="5" t="inlineStr"/>
       <c r="Q8" s="5" t="inlineStr"/>
       <c r="R8" s="5" t="inlineStr"/>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="50" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -1093,6 +1134,8 @@
       <c r="P9" s="5" t="inlineStr"/>
       <c r="Q9" s="5" t="inlineStr"/>
       <c r="R9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="50" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -1131,6 +1174,8 @@
       <c r="P10" s="5" t="inlineStr"/>
       <c r="Q10" s="5" t="inlineStr"/>
       <c r="R10" s="5" t="inlineStr"/>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
     </row>
     <row r="11" ht="50" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1169,6 +1214,8 @@
       <c r="P11" s="5" t="inlineStr"/>
       <c r="Q11" s="5" t="inlineStr"/>
       <c r="R11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
     </row>
     <row r="12" ht="50" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1206,6 +1253,8 @@
       <c r="P12" s="5" t="inlineStr"/>
       <c r="Q12" s="5" t="inlineStr"/>
       <c r="R12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr"/>
     </row>
     <row r="13" ht="50" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1243,6 +1292,8 @@
       <c r="P13" s="5" t="inlineStr"/>
       <c r="Q13" s="5" t="inlineStr"/>
       <c r="R13" s="5" t="inlineStr"/>
+      <c r="S13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr"/>
     </row>
     <row r="14" ht="50" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1272,6 +1323,8 @@
       <c r="P14" s="5" t="inlineStr"/>
       <c r="Q14" s="5" t="inlineStr"/>
       <c r="R14" s="5" t="inlineStr"/>
+      <c r="S14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr"/>
     </row>
     <row r="15" ht="50" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1301,6 +1354,8 @@
       <c r="P15" s="5" t="inlineStr"/>
       <c r="Q15" s="5" t="inlineStr"/>
       <c r="R15" s="5" t="inlineStr"/>
+      <c r="S15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr"/>
     </row>
     <row r="16" ht="50" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
@@ -1330,6 +1385,8 @@
       <c r="P16" s="5" t="inlineStr"/>
       <c r="Q16" s="5" t="inlineStr"/>
       <c r="R16" s="5" t="inlineStr"/>
+      <c r="S16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr"/>
     </row>
     <row r="17" ht="50" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1359,14 +1416,17 @@
       <c r="P17" s="5" t="inlineStr"/>
       <c r="Q17" s="5" t="inlineStr"/>
       <c r="R17" s="5" t="inlineStr"/>
+      <c r="S17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="Q1:R1"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="S1:T1"/>
     <mergeCell ref="O1:P1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="M1:N1"/>

--- a/HarmonyOS_API汇总.xlsx
+++ b/HarmonyOS_API汇总.xlsx
@@ -521,13 +521,13 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>辅助功能</t>
+          <t>桌面设置</t>
         </is>
       </c>
       <c r="N1" s="2" t="n"/>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>桌面设置</t>
+          <t>辅助功能</t>
         </is>
       </c>
       <c r="P1" s="2" t="n"/>
@@ -714,21 +714,10 @@
       </c>
       <c r="M3" s="4" t="inlineStr">
         <is>
-          <t>放大手势</t>
+          <t>桌面设置(下滑/上滑/布局/自动对齐/锁定布局)</t>
         </is>
       </c>
       <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>query_zoom_gesture()
-set_zoom_gesture('on'/'off')</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>桌面设置(下滑/上滑/布局/自动对齐/锁定布局)</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>query_desktop_setting(item)
 set_desktop_setting(item, 'on'/'off')
@@ -736,6 +725,17 @@
   item: swipe_down/swipe_up/layout/auto_align/lock_layout</t>
         </is>
       </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>放大手势</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>query_zoom_gesture()
+set_zoom_gesture('on'/'off')</t>
+        </is>
+      </c>
       <c r="Q3" s="4" t="inlineStr">
         <is>
           <t>省电模式</t>
@@ -827,17 +827,28 @@
       </c>
       <c r="M4" s="4" t="inlineStr">
         <is>
+          <t>桌面主题</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>is_theme_visible(theme_name) → bool
+is_theme_detail(theme_name) → bool
+  不导航，只检查当前页面
+  如 星蕴金/星蕴蓝/织锦金/元气心情</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
           <t>颜色反转</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>query_color_inversion()
 set_color_inversion('on'/'off')</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
       <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr"/>
       <c r="S4" s="5" t="inlineStr"/>
